--- a/data/source/weekly/cs-en-us-048pct.xlsx
+++ b/data/source/weekly/cs-en-us-048pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -854,17 +854,17 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="14">
         <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="14">
-        <v>2</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="15">
+        <v>100</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
+        <v>200</v>
+      </c>
+      <c r="I15" s="14">
+        <v>4</v>
+      </c>
+      <c r="J15" s="14">
+        <v>2</v>
+      </c>
+      <c r="K15" s="15">
+        <v>100</v>
+      </c>
+      <c r="L15" s="15">
+        <v>100</v>
+      </c>
+      <c r="M15" s="15">
         <v>0</v>
       </c>
-      <c r="I15" s="14">
-        <v>1</v>
-      </c>
-      <c r="J15" s="14">
-        <v>1</v>
-      </c>
-      <c r="K15" s="15">
-        <v>0</v>
-      </c>
-      <c r="L15" s="15">
-        <v>-50</v>
-      </c>
-      <c r="M15" s="15">
-        <v>-75</v>
-      </c>
       <c r="N15" s="15">
-        <v>-85.714285714285</v>
+        <v>-42.857142857142</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E16" s="15">
-        <v>75</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G16" s="14">
         <v>23</v>
       </c>
       <c r="H16" s="15">
-        <v>-13.043478260869</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="I16" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J16" s="14">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K16" s="15">
-        <v>-13.513513513513</v>
+        <v>-20</v>
       </c>
       <c r="L16" s="15">
-        <v>-46.666666666666</v>
+        <v>-44.615384615384</v>
       </c>
       <c r="M16" s="15">
-        <v>-21.951219512195</v>
+        <v>-23.404255319148</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.464788732394</v>
+        <v>-77.358490566037</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>-55</v>
+        <v>-20</v>
       </c>
       <c r="F17" s="14">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G17" s="14">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H17" s="15">
-        <v>-32.352941176470</v>
+        <v>-21.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="J17" s="14">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="K17" s="15">
-        <v>-31.111111111111</v>
+        <v>-29</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.823529411764</v>
+        <v>-16.470588235294</v>
       </c>
       <c r="M17" s="15">
-        <v>93.75</v>
+        <v>102.857142857143</v>
       </c>
       <c r="N17" s="15">
-        <v>8.771929824561</v>
+        <v>14.516129032258</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D18" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-44.444444444444</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F18" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G18" s="14">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H18" s="15">
-        <v>4.347826086956</v>
+        <v>50</v>
       </c>
       <c r="I18" s="14">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="J18" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K18" s="15">
-        <v>12.121212121212</v>
+        <v>25</v>
       </c>
       <c r="L18" s="15">
-        <v>-13.953488372093</v>
+        <v>-10</v>
       </c>
       <c r="M18" s="15">
-        <v>76.190476190476</v>
+        <v>80</v>
       </c>
       <c r="N18" s="15">
-        <v>-75</v>
+        <v>-75.274725274725</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>8.333333333333</v>
+        <v>80</v>
       </c>
       <c r="F19" s="14">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G19" s="14">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H19" s="15">
-        <v>7.142857142857</v>
+        <v>14.634146341463</v>
       </c>
       <c r="I19" s="14">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="J19" s="14">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="K19" s="15">
-        <v>-3.278688524590</v>
+        <v>8.450704225352</v>
       </c>
       <c r="L19" s="15">
-        <v>-9.230769230769</v>
+        <v>-6.097560975609</v>
       </c>
       <c r="M19" s="15">
-        <v>90.322580645161</v>
+        <v>120</v>
       </c>
       <c r="N19" s="15">
-        <v>9.259259259259</v>
+        <v>35.087719298245</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
         <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="F20" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G20" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H20" s="15">
-        <v>-6.25</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="I20" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J20" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K20" s="15">
-        <v>-21.739130434782</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L20" s="15">
-        <v>-25</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="M20" s="15">
-        <v>80</v>
+        <v>61.538461538461</v>
       </c>
       <c r="N20" s="15">
-        <v>-76.315789473684</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D21" s="17">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E21" s="18">
-        <v>-22</v>
+        <v>13.888888888888</v>
       </c>
       <c r="F21" s="17">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G21" s="17">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.714285714285</v>
+        <v>-4.968944099378</v>
       </c>
       <c r="I21" s="17">
-        <v>209</v>
+        <v>254</v>
       </c>
       <c r="J21" s="17">
-        <v>247</v>
+        <v>283</v>
       </c>
       <c r="K21" s="18">
-        <v>-15.384615384615</v>
+        <v>-10.247349823321</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.532319391635</v>
+        <v>-19.108280254777</v>
       </c>
       <c r="M21" s="18">
-        <v>50.359712230215</v>
+        <v>59.748427672956</v>
       </c>
       <c r="N21" s="18">
-        <v>-57.084188911704</v>
+        <v>-54.234234234234</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,8 +1188,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="14">
-        <v>1</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1206,8 +1206,8 @@
       <c r="K22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L22" s="13" t="s">
-        <v>21</v>
+      <c r="L22" s="15">
+        <v>0</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1229,8 +1229,8 @@
       <c r="E23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="13" t="s">
-        <v>20</v>
+      <c r="F23" s="14">
+        <v>1</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>20</v>
@@ -1239,7 +1239,7 @@
         <v>21</v>
       </c>
       <c r="I23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" s="13" t="s">
         <v>20</v>
@@ -1248,10 +1248,10 @@
         <v>21</v>
       </c>
       <c r="L23" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="M23" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>-10.714285714285</v>
+        <v>5.882352941176</v>
       </c>
       <c r="F24" s="14">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="G24" s="14">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="H24" s="15">
-        <v>-22.5</v>
+        <v>-25.438596491228</v>
       </c>
       <c r="I24" s="14">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="J24" s="14">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="K24" s="15">
-        <v>-14.743589743589</v>
+        <v>-13.872832369942</v>
       </c>
       <c r="L24" s="15">
-        <v>23.148148148148</v>
+        <v>18.253968253968</v>
       </c>
       <c r="M24" s="15">
-        <v>38.541666666666</v>
+        <v>30.701754385964</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>-33.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F25" s="14">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G25" s="14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H25" s="15">
-        <v>-52.777777777777</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="I25" s="14">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J25" s="14">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K25" s="15">
-        <v>-48.888888888888</v>
+        <v>-35.416666666666</v>
       </c>
       <c r="L25" s="15">
-        <v>-32.352941176470</v>
+        <v>-16.216216216216</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="F26" s="14">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G26" s="14">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H26" s="15">
-        <v>-6.25</v>
+        <v>-21.311475409836</v>
       </c>
       <c r="I26" s="14">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J26" s="14">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="K26" s="15">
-        <v>2.325581395348</v>
+        <v>-4.950495049504</v>
       </c>
       <c r="L26" s="15">
-        <v>14.285714285714</v>
+        <v>-2.040816326530</v>
       </c>
       <c r="M26" s="15">
-        <v>6.024096385542</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="15">
+        <v>100</v>
       </c>
       <c r="F27" s="14">
+        <v>3</v>
+      </c>
+      <c r="G27" s="14">
         <v>1</v>
       </c>
-      <c r="G27" s="14">
-        <v>3</v>
-      </c>
       <c r="H27" s="15">
-        <v>-66.666666666666</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,13 +1426,13 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
         <v>7</v>
@@ -1444,16 +1444,16 @@
         <v>75</v>
       </c>
       <c r="I28" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>66.666666666666</v>
+        <v>37.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,20 +1469,20 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="14">
         <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>1</v>
@@ -1494,13 +1494,13 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M29" s="15">
-        <v>-80</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-91.666666666666</v>
+        <v>-93.333333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,20 +1510,20 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="14">
         <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>1</v>
@@ -1535,21 +1535,21 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>-80</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-90.909090909090</v>
+        <v>-92.857142857142</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-048pct.xlsx
+++ b/data/source/weekly/cs-en-us-048pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -854,17 +854,17 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -873,7 +873,7 @@
         <v>20</v>
       </c>
       <c r="J14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" s="15">
         <v>-100</v>
@@ -892,32 +892,32 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L15" s="15">
         <v>100</v>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F16" s="14">
         <v>17</v>
       </c>
       <c r="G16" s="14">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H16" s="15">
-        <v>-26.086956521739</v>
+        <v>-41.379310344827</v>
       </c>
       <c r="I16" s="14">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="J16" s="14">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="K16" s="15">
-        <v>-20</v>
+        <v>-24.074074074074</v>
       </c>
       <c r="L16" s="15">
-        <v>-44.615384615384</v>
+        <v>-43.055555555555</v>
       </c>
       <c r="M16" s="15">
-        <v>-23.404255319148</v>
+        <v>-19.607843137254</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.358490566037</v>
+        <v>-77.222222222222</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
         <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>-20</v>
+        <v>30</v>
       </c>
       <c r="F17" s="14">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G17" s="14">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H17" s="15">
-        <v>-21.666666666666</v>
+        <v>-12.727272727272</v>
       </c>
       <c r="I17" s="14">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="J17" s="14">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="K17" s="15">
-        <v>-29</v>
+        <v>-23.636363636363</v>
       </c>
       <c r="L17" s="15">
-        <v>-16.470588235294</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="M17" s="15">
-        <v>102.857142857143</v>
+        <v>110</v>
       </c>
       <c r="N17" s="15">
-        <v>14.516129032258</v>
+        <v>13.513513513513</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>166.666666666667</v>
+        <v>80</v>
       </c>
       <c r="F18" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G18" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>50</v>
+        <v>57.894736842105</v>
       </c>
       <c r="I18" s="14">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="J18" s="14">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="K18" s="15">
-        <v>25</v>
+        <v>34.146341463414</v>
       </c>
       <c r="L18" s="15">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="M18" s="15">
-        <v>80</v>
+        <v>77.419354838709</v>
       </c>
       <c r="N18" s="15">
-        <v>-75.274725274725</v>
+        <v>-73.557692307692</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G19" s="14">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H19" s="15">
-        <v>14.634146341463</v>
+        <v>22.857142857142</v>
       </c>
       <c r="I19" s="14">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J19" s="14">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="K19" s="15">
-        <v>8.450704225352</v>
+        <v>8.974358974358</v>
       </c>
       <c r="L19" s="15">
-        <v>-6.097560975609</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="M19" s="15">
-        <v>120</v>
+        <v>129.72972972973</v>
       </c>
       <c r="N19" s="15">
-        <v>35.087719298245</v>
+        <v>26.865671641791</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>-75</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F20" s="14">
         <v>12</v>
       </c>
       <c r="G20" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H20" s="15">
-        <v>-29.411764705882</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I20" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J20" s="14">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="K20" s="15">
-        <v>-22.222222222222</v>
+        <v>-26.470588235294</v>
       </c>
       <c r="L20" s="15">
-        <v>-27.586206896551</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M20" s="15">
-        <v>61.538461538461</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-75</v>
+        <v>-73.958333333333</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D21" s="17">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E21" s="18">
-        <v>13.888888888888</v>
+        <v>-5</v>
       </c>
       <c r="F21" s="17">
         <v>153</v>
       </c>
       <c r="G21" s="17">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H21" s="18">
-        <v>-4.968944099378</v>
+        <v>-6.134969325153</v>
       </c>
       <c r="I21" s="17">
-        <v>254</v>
+        <v>294</v>
       </c>
       <c r="J21" s="17">
-        <v>283</v>
+        <v>323</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.247349823321</v>
+        <v>-8.978328173374</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.108280254777</v>
+        <v>-15.517241379310</v>
       </c>
       <c r="M21" s="18">
-        <v>59.748427672956</v>
+        <v>65.168539325842</v>
       </c>
       <c r="N21" s="18">
-        <v>-54.234234234234</v>
+        <v>-53.846153846153</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,8 +1188,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,7 +1198,7 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" s="13" t="s">
         <v>20</v>
@@ -1207,7 +1207,7 @@
         <v>21</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>21</v>
@@ -1223,35 +1223,35 @@
       <c r="C23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>0</v>
       </c>
       <c r="F23" s="14">
+        <v>2</v>
+      </c>
+      <c r="G23" s="14">
         <v>1</v>
       </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
+      <c r="H23" s="15">
+        <v>100</v>
       </c>
       <c r="I23" s="14">
-        <v>2</v>
-      </c>
-      <c r="J23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K23" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="J23" s="14">
+        <v>1</v>
+      </c>
+      <c r="K23" s="15">
+        <v>200</v>
       </c>
       <c r="L23" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M23" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E24" s="15">
-        <v>5.882352941176</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F24" s="14">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G24" s="14">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="H24" s="15">
-        <v>-25.438596491228</v>
+        <v>-20.192307692307</v>
       </c>
       <c r="I24" s="14">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="J24" s="14">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="K24" s="15">
-        <v>-13.872832369942</v>
+        <v>-14.358974358974</v>
       </c>
       <c r="L24" s="15">
-        <v>18.253968253968</v>
+        <v>9.150326797385</v>
       </c>
       <c r="M24" s="15">
-        <v>30.701754385964</v>
+        <v>26.515151515151</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>4</v>
+      </c>
+      <c r="D25" s="14">
         <v>8</v>
       </c>
-      <c r="D25" s="14">
-        <v>3</v>
-      </c>
       <c r="E25" s="15">
-        <v>166.666666666667</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
         <v>22</v>
       </c>
       <c r="G25" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H25" s="15">
-        <v>-35.294117647058</v>
+        <v>-40.540540540540</v>
       </c>
       <c r="I25" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J25" s="14">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="K25" s="15">
-        <v>-35.416666666666</v>
+        <v>-37.5</v>
       </c>
       <c r="L25" s="15">
-        <v>-16.216216216216</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E26" s="15">
-        <v>-40</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F26" s="14">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G26" s="14">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H26" s="15">
-        <v>-21.311475409836</v>
+        <v>-10.169491525423</v>
       </c>
       <c r="I26" s="14">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="J26" s="14">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="K26" s="15">
-        <v>-4.950495049504</v>
+        <v>-2.608695652173</v>
       </c>
       <c r="L26" s="15">
-        <v>-2.040816326530</v>
+        <v>-4.273504273504</v>
       </c>
       <c r="M26" s="15">
-        <v>-5.882352941176</v>
+        <v>0</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I27" s="14">
         <v>4</v>
       </c>
       <c r="J27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L27" s="15">
         <v>33.333333333333</v>
@@ -1425,23 +1425,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-50</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
         <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
         <v>11</v>
@@ -1453,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>37.5</v>
+        <v>22.222222222222</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,90 +1466,90 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="14">
+        <v>3</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="I29" s="14">
         <v>2</v>
       </c>
-      <c r="H29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I29" s="14">
-        <v>1</v>
-      </c>
       <c r="J29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K29" s="15">
+        <v>-50</v>
+      </c>
+      <c r="L29" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="M29" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="L29" s="15">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="M29" s="15">
-        <v>-83.333333333333</v>
-      </c>
       <c r="N29" s="15">
-        <v>-93.333333333333</v>
+        <v>-88.235294117647</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
+      </c>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="14">
+        <v>3</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="I30" s="14">
         <v>2</v>
       </c>
-      <c r="H30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I30" s="14">
-        <v>1</v>
-      </c>
       <c r="J30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" s="15">
+        <v>-50</v>
+      </c>
+      <c r="L30" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="M30" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="L30" s="15">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="M30" s="15">
-        <v>-83.333333333333</v>
-      </c>
       <c r="N30" s="15">
-        <v>-92.857142857142</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1575,8 +1575,8 @@
       <c r="K31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+      <c r="L31" s="15">
+        <v>100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1634,8 +1634,8 @@
       <c r="K33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="15">
+        <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-048pct.xlsx
+++ b/data/source/weekly/cs-en-us-048pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -896,7 +896,7 @@
         <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
         <v>-100</v>
@@ -905,22 +905,22 @@
         <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>50</v>
+        <v>-25</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K15" s="15">
+        <v>-20</v>
+      </c>
+      <c r="L15" s="15">
         <v>33.333333333333</v>
-      </c>
-      <c r="L15" s="15">
-        <v>100</v>
       </c>
       <c r="M15" s="15">
         <v>0</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E16" s="15">
-        <v>-44.444444444444</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G16" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H16" s="15">
-        <v>-41.379310344827</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I16" s="14">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="J16" s="14">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="K16" s="15">
-        <v>-24.074074074074</v>
+        <v>-25.757575757575</v>
       </c>
       <c r="L16" s="15">
-        <v>-43.055555555555</v>
+        <v>-40.243902439024</v>
       </c>
       <c r="M16" s="15">
-        <v>-19.607843137254</v>
+        <v>-14.035087719298</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.222222222222</v>
+        <v>-76.328502415458</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E17" s="15">
-        <v>30</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="14">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G17" s="14">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H17" s="15">
-        <v>-12.727272727272</v>
+        <v>-29.629629629629</v>
       </c>
       <c r="I17" s="14">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="J17" s="14">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="K17" s="15">
-        <v>-23.636363636363</v>
+        <v>-25.806451612903</v>
       </c>
       <c r="L17" s="15">
-        <v>-9.677419354838</v>
+        <v>-12.380952380952</v>
       </c>
       <c r="M17" s="15">
-        <v>110</v>
+        <v>109.090909090909</v>
       </c>
       <c r="N17" s="15">
-        <v>13.513513513513</v>
+        <v>9.523809523809</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>80</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H18" s="15">
-        <v>57.894736842105</v>
+        <v>26.086956521739</v>
       </c>
       <c r="I18" s="14">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="J18" s="14">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K18" s="15">
-        <v>34.146341463414</v>
+        <v>31.914893617021</v>
       </c>
       <c r="L18" s="15">
-        <v>0</v>
+        <v>10.714285714285</v>
       </c>
       <c r="M18" s="15">
-        <v>77.419354838709</v>
+        <v>93.75</v>
       </c>
       <c r="N18" s="15">
-        <v>-73.557692307692</v>
+        <v>-74.273858921161</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F19" s="14">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G19" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H19" s="15">
-        <v>22.857142857142</v>
+        <v>35.897435897435</v>
       </c>
       <c r="I19" s="14">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="J19" s="14">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="K19" s="15">
-        <v>8.974358974358</v>
+        <v>12.5</v>
       </c>
       <c r="L19" s="15">
-        <v>-5.555555555555</v>
+        <v>-5.714285714285</v>
       </c>
       <c r="M19" s="15">
-        <v>129.72972972973</v>
+        <v>135.714285714286</v>
       </c>
       <c r="N19" s="15">
-        <v>26.865671641791</v>
+        <v>25.316455696202</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-42.857142857142</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G20" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H20" s="15">
-        <v>-42.857142857142</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="I20" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J20" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K20" s="15">
-        <v>-26.470588235294</v>
+        <v>-19.444444444444</v>
       </c>
       <c r="L20" s="15">
-        <v>-28.571428571428</v>
+        <v>-27.5</v>
       </c>
       <c r="M20" s="15">
-        <v>66.666666666666</v>
+        <v>81.25</v>
       </c>
       <c r="N20" s="15">
-        <v>-73.958333333333</v>
+        <v>-73.394495412844</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>38</v>
       </c>
       <c r="D21" s="17">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E21" s="18">
-        <v>-5</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="F21" s="17">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="G21" s="17">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="H21" s="18">
-        <v>-6.134969325153</v>
+        <v>-5.813953488372</v>
       </c>
       <c r="I21" s="17">
-        <v>294</v>
+        <v>335</v>
       </c>
       <c r="J21" s="17">
-        <v>323</v>
+        <v>369</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.978328173374</v>
+        <v>-9.214092140921</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.517241379310</v>
+        <v>-14.540816326530</v>
       </c>
       <c r="M21" s="18">
-        <v>65.168539325842</v>
+        <v>71.794871794871</v>
       </c>
       <c r="N21" s="18">
-        <v>-53.846153846153</v>
+        <v>-54.297407912687</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,32 +1182,32 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>2</v>
       </c>
-      <c r="J22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>21</v>
+      <c r="J22" s="14">
+        <v>1</v>
+      </c>
+      <c r="K22" s="15">
+        <v>100</v>
       </c>
       <c r="L22" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>21</v>
@@ -1223,35 +1223,35 @@
       <c r="C23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>0</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="14">
         <v>1</v>
       </c>
       <c r="H23" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J23" s="14">
         <v>1</v>
       </c>
       <c r="K23" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L23" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M23" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E24" s="15">
-        <v>-9.090909090909</v>
+        <v>38.461538461538</v>
       </c>
       <c r="F24" s="14">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G24" s="14">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="H24" s="15">
-        <v>-20.192307692307</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="J24" s="14">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="K24" s="15">
-        <v>-14.358974358974</v>
+        <v>-10.096153846153</v>
       </c>
       <c r="L24" s="15">
-        <v>9.150326797385</v>
+        <v>5.649717514124</v>
       </c>
       <c r="M24" s="15">
-        <v>26.515151515151</v>
+        <v>30.769230769230</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G25" s="14">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="H25" s="15">
-        <v>-40.540540540540</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J25" s="14">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K25" s="15">
-        <v>-37.5</v>
+        <v>-34.482758620689</v>
       </c>
       <c r="L25" s="15">
-        <v>-16.666666666666</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>14.285714285714</v>
+        <v>44.444444444444</v>
       </c>
       <c r="F26" s="14">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G26" s="14">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="H26" s="15">
-        <v>-10.169491525423</v>
+        <v>-3.921568627450</v>
       </c>
       <c r="I26" s="14">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="J26" s="14">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.608695652173</v>
+        <v>0</v>
       </c>
       <c r="L26" s="15">
-        <v>-4.273504273504</v>
+        <v>-12.056737588652</v>
       </c>
       <c r="M26" s="15">
-        <v>0</v>
+        <v>-6.766917293233</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>2</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
+        <v>25</v>
+      </c>
+      <c r="I27" s="14">
+        <v>6</v>
+      </c>
+      <c r="J27" s="14">
+        <v>7</v>
+      </c>
+      <c r="K27" s="15">
+        <v>-14.285714285714</v>
+      </c>
+      <c r="L27" s="15">
         <v>50</v>
-      </c>
-      <c r="I27" s="14">
-        <v>4</v>
-      </c>
-      <c r="J27" s="14">
-        <v>5</v>
-      </c>
-      <c r="K27" s="15">
-        <v>-20</v>
-      </c>
-      <c r="L27" s="15">
-        <v>33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>3</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>50</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
         <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J28" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>7.692307692307</v>
       </c>
       <c r="L28" s="15">
-        <v>22.222222222222</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,14 +1466,14 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="14">
         <v>1</v>
       </c>
       <c r="E29" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
@@ -1488,13 +1488,13 @@
         <v>2</v>
       </c>
       <c r="J29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K29" s="15">
+        <v>-60</v>
+      </c>
+      <c r="L29" s="15">
         <v>-50</v>
-      </c>
-      <c r="L29" s="15">
-        <v>-33.333333333333</v>
       </c>
       <c r="M29" s="15">
         <v>-66.666666666666</v>
@@ -1507,14 +1507,14 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="14">
         <v>1</v>
       </c>
       <c r="E30" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
@@ -1529,13 +1529,13 @@
         <v>2</v>
       </c>
       <c r="J30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K30" s="15">
+        <v>-60</v>
+      </c>
+      <c r="L30" s="15">
         <v>-50</v>
-      </c>
-      <c r="L30" s="15">
-        <v>-33.333333333333</v>
       </c>
       <c r="M30" s="15">
         <v>-66.666666666666</v>

--- a/data/source/weekly/cs-en-us-048pct.xlsx
+++ b/data/source/weekly/cs-en-us-048pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,32 +860,32 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="14">
         <v>3</v>
       </c>
       <c r="K14" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L14" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>-100</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -895,20 +895,20 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>2</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
@@ -923,7 +923,7 @@
         <v>33.333333333333</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="N15" s="15">
         <v>-50</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="F16" s="14">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G16" s="14">
         <v>33</v>
       </c>
       <c r="H16" s="15">
-        <v>-27.272727272727</v>
+        <v>-39.393939393939</v>
       </c>
       <c r="I16" s="14">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J16" s="14">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K16" s="15">
-        <v>-25.757575757575</v>
+        <v>-25.714285714285</v>
       </c>
       <c r="L16" s="15">
-        <v>-40.243902439024</v>
+        <v>-39.534883720930</v>
       </c>
       <c r="M16" s="15">
-        <v>-14.035087719298</v>
+        <v>-16.129032258064</v>
       </c>
       <c r="N16" s="15">
-        <v>-76.328502415458</v>
+        <v>-77.682403433476</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F17" s="14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G17" s="14">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="H17" s="15">
-        <v>-29.629629629629</v>
+        <v>-20</v>
       </c>
       <c r="I17" s="14">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="J17" s="14">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="K17" s="15">
-        <v>-25.806451612903</v>
+        <v>-25.925925925925</v>
       </c>
       <c r="L17" s="15">
-        <v>-12.380952380952</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="M17" s="15">
-        <v>109.090909090909</v>
+        <v>81.818181818181</v>
       </c>
       <c r="N17" s="15">
-        <v>9.523809523809</v>
+        <v>-1.960784313725</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>16.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="F18" s="14">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G18" s="14">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H18" s="15">
-        <v>26.086956521739</v>
+        <v>44.444444444444</v>
       </c>
       <c r="I18" s="14">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J18" s="14">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K18" s="15">
-        <v>31.914893617021</v>
+        <v>25.490196078431</v>
       </c>
       <c r="L18" s="15">
-        <v>10.714285714285</v>
+        <v>6.666666666666</v>
       </c>
       <c r="M18" s="15">
-        <v>93.75</v>
+        <v>82.857142857142</v>
       </c>
       <c r="N18" s="15">
-        <v>-74.273858921161</v>
+        <v>-76.208178438661</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E19" s="15">
-        <v>20</v>
+        <v>-18.75</v>
       </c>
       <c r="F19" s="14">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G19" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H19" s="15">
-        <v>35.897435897435</v>
+        <v>25.581395348837</v>
       </c>
       <c r="I19" s="14">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="J19" s="14">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="K19" s="15">
-        <v>12.5</v>
+        <v>8.653846153846</v>
       </c>
       <c r="L19" s="15">
-        <v>-5.714285714285</v>
+        <v>-3.418803418803</v>
       </c>
       <c r="M19" s="15">
-        <v>135.714285714286</v>
+        <v>140.425531914894</v>
       </c>
       <c r="N19" s="15">
-        <v>25.316455696202</v>
+        <v>29.885057471264</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G20" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H20" s="15">
-        <v>-11.764705882352</v>
+        <v>-12.5</v>
       </c>
       <c r="I20" s="14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J20" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K20" s="15">
-        <v>-19.444444444444</v>
+        <v>-12.820512820512</v>
       </c>
       <c r="L20" s="15">
-        <v>-27.5</v>
+        <v>-24.444444444444</v>
       </c>
       <c r="M20" s="15">
-        <v>81.25</v>
+        <v>78.947368421052</v>
       </c>
       <c r="N20" s="15">
-        <v>-73.394495412844</v>
+        <v>-70.940170940170</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>30</v>
+      </c>
+      <c r="D21" s="17">
         <v>38</v>
       </c>
-      <c r="D21" s="17">
-        <v>46</v>
-      </c>
       <c r="E21" s="18">
-        <v>-17.391304347826</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="F21" s="17">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="G21" s="17">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.813953488372</v>
+        <v>-4.375</v>
       </c>
       <c r="I21" s="17">
-        <v>335</v>
+        <v>368</v>
       </c>
       <c r="J21" s="17">
-        <v>369</v>
+        <v>407</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.214092140921</v>
+        <v>-9.582309582309</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.540816326530</v>
+        <v>-13.817330210772</v>
       </c>
       <c r="M21" s="18">
-        <v>71.794871794871</v>
+        <v>65.022421524663</v>
       </c>
       <c r="N21" s="18">
-        <v>-54.297407912687</v>
+        <v>-55.231143552311</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1192,19 +1192,19 @@
         <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
         <v>2</v>
       </c>
       <c r="J22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
         <v>0</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1251,7 +1251,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>38.461538461538</v>
+        <v>4.166666666666</v>
       </c>
       <c r="F24" s="14">
         <v>80</v>
       </c>
       <c r="G24" s="14">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H24" s="15">
-        <v>0</v>
+        <v>5.263157894736</v>
       </c>
       <c r="I24" s="14">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="J24" s="14">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="K24" s="15">
-        <v>-10.096153846153</v>
+        <v>-9.482758620689</v>
       </c>
       <c r="L24" s="15">
-        <v>5.649717514124</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M24" s="15">
-        <v>30.769230769230</v>
+        <v>40</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F25" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G25" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H25" s="15">
-        <v>0</v>
+        <v>29.411764705882</v>
       </c>
       <c r="I25" s="14">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="J25" s="14">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K25" s="15">
-        <v>-34.482758620689</v>
+        <v>-27.419354838709</v>
       </c>
       <c r="L25" s="15">
-        <v>-17.391304347826</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E26" s="15">
-        <v>44.444444444444</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F26" s="14">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G26" s="14">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="H26" s="15">
-        <v>-3.921568627450</v>
+        <v>-6.779661016949</v>
       </c>
       <c r="I26" s="14">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="J26" s="14">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="K26" s="15">
-        <v>0</v>
+        <v>-2.068965517241</v>
       </c>
       <c r="L26" s="15">
-        <v>-12.056737588652</v>
+        <v>-7.792207792207</v>
       </c>
       <c r="M26" s="15">
-        <v>-6.766917293233</v>
+        <v>-5.960264900662</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
-      </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
         <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>6</v>
@@ -1429,31 +1429,31 @@
         <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
         <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J28" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K28" s="15">
-        <v>7.692307692307</v>
+        <v>6.25</v>
       </c>
       <c r="L28" s="15">
-        <v>16.666666666666</v>
+        <v>41.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="14">
+        <v>2</v>
+      </c>
+      <c r="D29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>-66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J29" s="14">
         <v>5</v>
       </c>
       <c r="K29" s="15">
-        <v>-60</v>
+        <v>-20</v>
       </c>
       <c r="L29" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-88.235294117647</v>
+        <v>-76.470588235294</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="14">
+        <v>2</v>
+      </c>
+      <c r="D30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>-66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J30" s="14">
         <v>5</v>
       </c>
       <c r="K30" s="15">
-        <v>-60</v>
+        <v>-20</v>
       </c>
       <c r="L30" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-87.5</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-048pct.xlsx
+++ b/data/source/weekly/cs-en-us-048pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,28 +902,28 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
         <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
         <v>-50</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
         <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G16" s="14">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H16" s="15">
-        <v>-39.393939393939</v>
+        <v>-37.931034482758</v>
       </c>
       <c r="I16" s="14">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J16" s="14">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K16" s="15">
-        <v>-25.714285714285</v>
+        <v>-27.027027027027</v>
       </c>
       <c r="L16" s="15">
-        <v>-39.534883720930</v>
+        <v>-41.935483870967</v>
       </c>
       <c r="M16" s="15">
-        <v>-16.129032258064</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.682403433476</v>
+        <v>-78.313253012048</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E17" s="15">
-        <v>-27.272727272727</v>
+        <v>-31.25</v>
       </c>
       <c r="F17" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G17" s="14">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H17" s="15">
-        <v>-20</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="I17" s="14">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="J17" s="14">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="K17" s="15">
-        <v>-25.925925925925</v>
+        <v>-25.827814569536</v>
       </c>
       <c r="L17" s="15">
-        <v>-13.043478260869</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="M17" s="15">
-        <v>81.818181818181</v>
+        <v>69.696969696969</v>
       </c>
       <c r="N17" s="15">
-        <v>-1.960784313725</v>
+        <v>3.703703703703</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
         <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-75</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G18" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>44.444444444444</v>
+        <v>31.578947368421</v>
       </c>
       <c r="I18" s="14">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="J18" s="14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K18" s="15">
-        <v>25.490196078431</v>
+        <v>29.090909090909</v>
       </c>
       <c r="L18" s="15">
-        <v>6.666666666666</v>
+        <v>18.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>82.857142857142</v>
+        <v>73.170731707317</v>
       </c>
       <c r="N18" s="15">
-        <v>-76.208178438661</v>
+        <v>-76.094276094276</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15">
-        <v>-18.75</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G19" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H19" s="15">
-        <v>25.581395348837</v>
+        <v>2.222222222222</v>
       </c>
       <c r="I19" s="14">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="J19" s="14">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="K19" s="15">
-        <v>8.653846153846</v>
+        <v>7.758620689655</v>
       </c>
       <c r="L19" s="15">
-        <v>-3.418803418803</v>
+        <v>-3.100775193798</v>
       </c>
       <c r="M19" s="15">
-        <v>140.425531914894</v>
+        <v>150</v>
       </c>
       <c r="N19" s="15">
-        <v>29.885057471264</v>
+        <v>35.869565217391</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>5</v>
+      </c>
+      <c r="D20" s="14">
         <v>4</v>
       </c>
-      <c r="D20" s="14">
-        <v>3</v>
-      </c>
       <c r="E20" s="15">
-        <v>33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="F20" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G20" s="14">
         <v>16</v>
       </c>
       <c r="H20" s="15">
-        <v>-12.5</v>
+        <v>12.5</v>
       </c>
       <c r="I20" s="14">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J20" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K20" s="15">
-        <v>-12.820512820512</v>
+        <v>-9.302325581395</v>
       </c>
       <c r="L20" s="15">
-        <v>-24.444444444444</v>
+        <v>-20.408163265306</v>
       </c>
       <c r="M20" s="15">
-        <v>78.947368421052</v>
+        <v>105.263157894737</v>
       </c>
       <c r="N20" s="15">
-        <v>-70.940170940170</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D21" s="17">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E21" s="18">
-        <v>-21.052631578947</v>
+        <v>-12.5</v>
       </c>
       <c r="F21" s="17">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G21" s="17">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="H21" s="18">
-        <v>-4.375</v>
+        <v>-9.756097560975</v>
       </c>
       <c r="I21" s="17">
-        <v>368</v>
+        <v>407</v>
       </c>
       <c r="J21" s="17">
-        <v>407</v>
+        <v>447</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.582309582309</v>
+        <v>-8.948545861297</v>
       </c>
       <c r="L21" s="18">
-        <v>-13.817330210772</v>
+        <v>-11.328976034858</v>
       </c>
       <c r="M21" s="18">
-        <v>65.022421524663</v>
+        <v>66.803278688524</v>
       </c>
       <c r="N21" s="18">
-        <v>-55.231143552311</v>
+        <v>-54.372197309417</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="14">
+      <c r="C22" s="14">
         <v>1</v>
       </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
@@ -1198,16 +1198,16 @@
         <v>-50</v>
       </c>
       <c r="I22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" s="14">
         <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>21</v>
@@ -1230,13 +1230,13 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23" s="14">
         <v>1</v>
       </c>
       <c r="H23" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I23" s="14">
         <v>4</v>
@@ -1248,7 +1248,7 @@
         <v>300</v>
       </c>
       <c r="L23" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="M23" s="15">
         <v>100</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>4.166666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F24" s="14">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G24" s="14">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="H24" s="15">
-        <v>5.263157894736</v>
+        <v>-5.747126436781</v>
       </c>
       <c r="I24" s="14">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="J24" s="14">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.482758620689</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="L24" s="15">
-        <v>11.111111111111</v>
+        <v>10.047846889952</v>
       </c>
       <c r="M24" s="15">
-        <v>40</v>
+        <v>44.654088050314</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
         <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G25" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H25" s="15">
-        <v>29.411764705882</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J25" s="14">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K25" s="15">
-        <v>-27.419354838709</v>
+        <v>-25.757575757575</v>
       </c>
       <c r="L25" s="15">
-        <v>-11.764705882352</v>
+        <v>-7.547169811320</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>18</v>
       </c>
       <c r="D26" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E26" s="15">
-        <v>-14.285714285714</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="F26" s="14">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G26" s="14">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H26" s="15">
-        <v>-6.779661016949</v>
+        <v>1.587301587301</v>
       </c>
       <c r="I26" s="14">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="J26" s="14">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.068965517241</v>
+        <v>-2.439024390243</v>
       </c>
       <c r="L26" s="15">
-        <v>-7.792207792207</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M26" s="15">
-        <v>-5.960264900662</v>
+        <v>-1.840490797546</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
         <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="14">
         <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="F28" s="14">
         <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I28" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J28" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K28" s="15">
-        <v>6.25</v>
+        <v>-10</v>
       </c>
       <c r="L28" s="15">
-        <v>41.666666666666</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>2</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-33.333333333333</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="N29" s="15">
         <v>-76.470588235294</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>2</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1538,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="15">
         <v>-75</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-048pct.xlsx
+++ b/data/source/weekly/cs-en-us-048pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -863,11 +863,11 @@
       <c r="F14" s="14">
         <v>1</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>0</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -885,21 +885,21 @@
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -911,22 +911,22 @@
         <v>-66.666666666666</v>
       </c>
       <c r="I15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="15">
         <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N15" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>-37.5</v>
       </c>
       <c r="F16" s="14">
         <v>18</v>
       </c>
       <c r="G16" s="14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H16" s="15">
-        <v>-37.931034482758</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I16" s="14">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J16" s="14">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K16" s="15">
-        <v>-27.027027027027</v>
+        <v>-26.829268292682</v>
       </c>
       <c r="L16" s="15">
-        <v>-41.935483870967</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="M16" s="15">
-        <v>-14.285714285714</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="N16" s="15">
-        <v>-78.313253012048</v>
+        <v>-78.102189781021</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>-31.25</v>
+        <v>44.444444444444</v>
       </c>
       <c r="F17" s="14">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G17" s="14">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H17" s="15">
-        <v>-23.529411764705</v>
+        <v>-20</v>
       </c>
       <c r="I17" s="14">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="J17" s="14">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="K17" s="15">
-        <v>-25.827814569536</v>
+        <v>-21.25</v>
       </c>
       <c r="L17" s="15">
-        <v>-9.677419354838</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="M17" s="15">
-        <v>69.696969696969</v>
+        <v>70.270270270270</v>
       </c>
       <c r="N17" s="15">
-        <v>3.703703703703</v>
+        <v>2.439024390243</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
         <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F18" s="14">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H18" s="15">
-        <v>31.578947368421</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I18" s="14">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J18" s="14">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K18" s="15">
-        <v>29.090909090909</v>
+        <v>28.813559322033</v>
       </c>
       <c r="L18" s="15">
-        <v>18.333333333333</v>
+        <v>15.151515151515</v>
       </c>
       <c r="M18" s="15">
-        <v>73.170731707317</v>
+        <v>68.888888888888</v>
       </c>
       <c r="N18" s="15">
-        <v>-76.094276094276</v>
+        <v>-76.543209876543</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E19" s="15">
-        <v>-16.666666666666</v>
+        <v>18.75</v>
       </c>
       <c r="F19" s="14">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G19" s="14">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="H19" s="15">
-        <v>2.222222222222</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="J19" s="14">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="K19" s="15">
-        <v>7.758620689655</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L19" s="15">
-        <v>-3.100775193798</v>
+        <v>0</v>
       </c>
       <c r="M19" s="15">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="N19" s="15">
-        <v>35.869565217391</v>
+        <v>41.584158415841</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="F20" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G20" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H20" s="15">
-        <v>12.5</v>
+        <v>72.727272727272</v>
       </c>
       <c r="I20" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J20" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K20" s="15">
-        <v>-9.302325581395</v>
+        <v>-4.444444444444</v>
       </c>
       <c r="L20" s="15">
-        <v>-20.408163265306</v>
+        <v>-17.307692307692</v>
       </c>
       <c r="M20" s="15">
-        <v>105.263157894737</v>
+        <v>104.761904761905</v>
       </c>
       <c r="N20" s="15">
-        <v>-70</v>
+        <v>-67.910447761194</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D21" s="17">
         <v>40</v>
       </c>
       <c r="E21" s="18">
-        <v>-12.5</v>
+        <v>17.5</v>
       </c>
       <c r="F21" s="17">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="G21" s="17">
         <v>164</v>
       </c>
       <c r="H21" s="18">
-        <v>-9.756097560975</v>
+        <v>-6.707317073170</v>
       </c>
       <c r="I21" s="17">
-        <v>407</v>
+        <v>455</v>
       </c>
       <c r="J21" s="17">
-        <v>447</v>
+        <v>487</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.948545861297</v>
+        <v>-6.570841889117</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.328976034858</v>
+        <v>-10.433070866141</v>
       </c>
       <c r="M21" s="18">
-        <v>66.803278688524</v>
+        <v>69.144981412639</v>
       </c>
       <c r="N21" s="18">
-        <v>-54.372197309417</v>
+        <v>-53.237410071942</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1230,13 +1230,13 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
-      </c>
-      <c r="G23" s="14">
         <v>1</v>
       </c>
-      <c r="H23" s="15">
-        <v>100</v>
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I23" s="14">
         <v>4</v>
@@ -1248,7 +1248,7 @@
         <v>300</v>
       </c>
       <c r="L23" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M23" s="15">
         <v>100</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E24" s="15">
-        <v>-28.571428571428</v>
+        <v>-15.151515151515</v>
       </c>
       <c r="F24" s="14">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G24" s="14">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="H24" s="15">
-        <v>-5.747126436781</v>
+        <v>-10.204081632653</v>
       </c>
       <c r="I24" s="14">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="J24" s="14">
-        <v>260</v>
+        <v>293</v>
       </c>
       <c r="K24" s="15">
-        <v>-11.538461538461</v>
+        <v>-12.286689419795</v>
       </c>
       <c r="L24" s="15">
-        <v>10.047846889952</v>
+        <v>10.775862068965</v>
       </c>
       <c r="M24" s="15">
-        <v>44.654088050314</v>
+        <v>41.988950276243</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G25" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H25" s="15">
-        <v>0</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="I25" s="14">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J25" s="14">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="K25" s="15">
-        <v>-25.757575757575</v>
+        <v>-30.666666666666</v>
       </c>
       <c r="L25" s="15">
-        <v>-7.547169811320</v>
+        <v>-8.771929824561</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D26" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E26" s="15">
-        <v>-5.263157894736</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="G26" s="14">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="H26" s="15">
-        <v>1.587301587301</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="J26" s="14">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.439024390243</v>
+        <v>-2.139037433155</v>
       </c>
       <c r="L26" s="15">
-        <v>-9.090909090909</v>
+        <v>-7.106598984771</v>
       </c>
       <c r="M26" s="15">
-        <v>-1.840490797546</v>
+        <v>1.666666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L27" s="15">
-        <v>75</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>-75</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H28" s="15">
-        <v>-22.222222222222</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J28" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K28" s="15">
-        <v>-10</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="L28" s="15">
-        <v>28.571428571428</v>
+        <v>18.75</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1476,31 +1476,31 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
+        <v>2</v>
+      </c>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>100</v>
+      </c>
+      <c r="I29" s="14">
         <v>3</v>
-      </c>
-      <c r="G29" s="14">
-        <v>2</v>
-      </c>
-      <c r="H29" s="15">
-        <v>50</v>
-      </c>
-      <c r="I29" s="14">
-        <v>4</v>
       </c>
       <c r="J29" s="14">
         <v>5</v>
       </c>
       <c r="K29" s="15">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="L29" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="M29" s="15">
-        <v>-55.555555555555</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="N29" s="15">
-        <v>-76.470588235294</v>
+        <v>-84.210526315789</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1517,31 +1517,31 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
+        <v>2</v>
+      </c>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>100</v>
+      </c>
+      <c r="I30" s="14">
         <v>3</v>
-      </c>
-      <c r="G30" s="14">
-        <v>2</v>
-      </c>
-      <c r="H30" s="15">
-        <v>50</v>
-      </c>
-      <c r="I30" s="14">
-        <v>4</v>
       </c>
       <c r="J30" s="14">
         <v>5</v>
       </c>
       <c r="K30" s="15">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="M30" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-75</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-048pct.xlsx
+++ b/data/source/weekly/cs-en-us-048pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -885,48 +885,48 @@
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>-85.714285714285</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
+        <v>3</v>
+      </c>
+      <c r="G15" s="14">
         <v>1</v>
       </c>
-      <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>1</v>
-      </c>
-      <c r="G15" s="14">
-        <v>3</v>
-      </c>
       <c r="H15" s="15">
-        <v>-66.666666666666</v>
+        <v>200</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J15" s="14">
         <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="M15" s="15">
-        <v>20</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>-37.5</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F16" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G16" s="14">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H16" s="15">
-        <v>-35.714285714285</v>
+        <v>-32</v>
       </c>
       <c r="I16" s="14">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="J16" s="14">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K16" s="15">
-        <v>-26.829268292682</v>
+        <v>-26.373626373626</v>
       </c>
       <c r="L16" s="15">
-        <v>-42.307692307692</v>
+        <v>-40.707964601769</v>
       </c>
       <c r="M16" s="15">
-        <v>-13.043478260869</v>
+        <v>-12.987012987013</v>
       </c>
       <c r="N16" s="15">
-        <v>-78.102189781021</v>
+        <v>-77.364864864864</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E17" s="15">
-        <v>44.444444444444</v>
+        <v>6.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G17" s="14">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H17" s="15">
-        <v>-20</v>
+        <v>-3.921568627450</v>
       </c>
       <c r="I17" s="14">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="J17" s="14">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="K17" s="15">
-        <v>-21.25</v>
+        <v>-19.428571428571</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.695652173913</v>
+        <v>-7.236842105263</v>
       </c>
       <c r="M17" s="15">
-        <v>70.270270270270</v>
+        <v>80.769230769230</v>
       </c>
       <c r="N17" s="15">
-        <v>2.439024390243</v>
+        <v>5.223880597014</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E18" s="15">
-        <v>25</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F18" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G18" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>11.111111111111</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="I18" s="14">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J18" s="14">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="K18" s="15">
-        <v>28.813559322033</v>
+        <v>25.757575757575</v>
       </c>
       <c r="L18" s="15">
-        <v>15.151515151515</v>
+        <v>16.901408450704</v>
       </c>
       <c r="M18" s="15">
-        <v>68.888888888888</v>
+        <v>72.916666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-76.543209876543</v>
+        <v>-75.872093023255</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>18.75</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F19" s="14">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G19" s="14">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I19" s="14">
+        <v>152</v>
+      </c>
+      <c r="J19" s="14">
         <v>143</v>
       </c>
-      <c r="J19" s="14">
-        <v>132</v>
-      </c>
       <c r="K19" s="15">
-        <v>8.333333333333</v>
+        <v>6.293706293706</v>
       </c>
       <c r="L19" s="15">
-        <v>0</v>
+        <v>-2.564102564102</v>
       </c>
       <c r="M19" s="15">
-        <v>160</v>
+        <v>153.333333333333</v>
       </c>
       <c r="N19" s="15">
-        <v>41.584158415841</v>
+        <v>38.181818181818</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>150</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F20" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G20" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H20" s="15">
-        <v>72.727272727272</v>
+        <v>43.75</v>
       </c>
       <c r="I20" s="14">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="J20" s="14">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="K20" s="15">
-        <v>-4.444444444444</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-17.307692307692</v>
+        <v>-5.454545454545</v>
       </c>
       <c r="M20" s="15">
-        <v>104.761904761905</v>
+        <v>147.619047619048</v>
       </c>
       <c r="N20" s="15">
-        <v>-67.910447761194</v>
+        <v>-65.100671140939</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D21" s="17">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E21" s="18">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="G21" s="17">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H21" s="18">
-        <v>-6.707317073170</v>
+        <v>-3.592814371257</v>
       </c>
       <c r="I21" s="17">
-        <v>455</v>
+        <v>504</v>
       </c>
       <c r="J21" s="17">
-        <v>487</v>
+        <v>536</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.570841889117</v>
+        <v>-5.970149253731</v>
       </c>
       <c r="L21" s="18">
-        <v>-10.433070866141</v>
+        <v>-8.860759493670</v>
       </c>
       <c r="M21" s="18">
-        <v>69.144981412639</v>
+        <v>73.793103448275</v>
       </c>
       <c r="N21" s="18">
-        <v>-53.237410071942</v>
+        <v>-52.136752136752</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1192,10 +1192,10 @@
         <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>3</v>
@@ -1209,8 +1209,8 @@
       <c r="L22" s="15">
         <v>50</v>
       </c>
-      <c r="M22" s="13" t="s">
-        <v>21</v>
+      <c r="M22" s="15">
+        <v>200</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1239,19 +1239,19 @@
         <v>21</v>
       </c>
       <c r="I23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23" s="14">
         <v>1</v>
       </c>
       <c r="K23" s="15">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="L23" s="15">
-        <v>-33.333333333333</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M23" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>24</v>
+      </c>
+      <c r="D24" s="14">
         <v>28</v>
       </c>
-      <c r="D24" s="14">
-        <v>33</v>
-      </c>
       <c r="E24" s="15">
-        <v>-15.151515151515</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F24" s="14">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G24" s="14">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="H24" s="15">
-        <v>-10.204081632653</v>
+        <v>-14.159292035398</v>
       </c>
       <c r="I24" s="14">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="J24" s="14">
-        <v>293</v>
+        <v>321</v>
       </c>
       <c r="K24" s="15">
-        <v>-12.286689419795</v>
+        <v>-12.461059190031</v>
       </c>
       <c r="L24" s="15">
-        <v>10.775862068965</v>
+        <v>8.076923076923</v>
       </c>
       <c r="M24" s="15">
-        <v>41.988950276243</v>
+        <v>43.367346938775</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>-66.666666666666</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F25" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G25" s="14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H25" s="15">
-        <v>-15.789473684210</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J25" s="14">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="K25" s="15">
-        <v>-30.666666666666</v>
+        <v>-32.926829268292</v>
       </c>
       <c r="L25" s="15">
-        <v>-8.771929824561</v>
+        <v>-12.698412698412</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D26" s="14">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>56.25</v>
       </c>
       <c r="F26" s="14">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="G26" s="14">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H26" s="15">
-        <v>0</v>
+        <v>6.329113924050</v>
       </c>
       <c r="I26" s="14">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="J26" s="14">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.139037433155</v>
+        <v>2.955665024630</v>
       </c>
       <c r="L26" s="15">
-        <v>-7.106598984771</v>
+        <v>-1.415094339622</v>
       </c>
       <c r="M26" s="15">
-        <v>1.666666666666</v>
+        <v>7.179487179487</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="14">
+      <c r="C27" s="14">
         <v>2</v>
       </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-25</v>
+        <v>50</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
         <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>-11.111111111111</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L27" s="15">
-        <v>33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="14">
-        <v>3</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-33.333333333333</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>-25</v>
+        <v>-30</v>
       </c>
       <c r="I28" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J28" s="14">
         <v>23</v>
       </c>
       <c r="K28" s="15">
-        <v>-17.391304347826</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="L28" s="15">
-        <v>18.75</v>
+        <v>25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>2</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,39 +1476,39 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
-      </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>100</v>
+        <v>4</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J29" s="14">
         <v>5</v>
       </c>
       <c r="K29" s="15">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-72.727272727272</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-84.210526315789</v>
+        <v>-77.272727272727</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1517,31 +1517,31 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
-      </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>100</v>
+        <v>3</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" s="14">
         <v>5</v>
       </c>
       <c r="K30" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="L30" s="15">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="M30" s="15">
-        <v>-66.666666666666</v>
+        <v>-60</v>
       </c>
       <c r="N30" s="15">
-        <v>-83.333333333333</v>
+        <v>-80.952380952380</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-048pct.xlsx
+++ b/data/source/weekly/cs-en-us-048pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -854,79 +854,79 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="14">
+      <c r="G14" s="14">
         <v>1</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
       </c>
       <c r="J14" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="L14" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>-90</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
-      </c>
-      <c r="D15" s="13" t="s">
+      <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>3</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>200</v>
+        <v>-25</v>
       </c>
       <c r="I15" s="14">
         <v>8</v>
       </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K15" s="15">
+        <v>-11.111111111111</v>
+      </c>
+      <c r="L15" s="15">
         <v>33.333333333333</v>
       </c>
-      <c r="L15" s="15">
-        <v>60</v>
-      </c>
       <c r="M15" s="15">
-        <v>33.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="N15" s="15">
-        <v>-20</v>
+        <v>-27.272727272727</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
         <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>-22.222222222222</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F16" s="14">
         <v>17</v>
       </c>
       <c r="G16" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H16" s="15">
-        <v>-32</v>
+        <v>-43.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J16" s="14">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="K16" s="15">
-        <v>-26.373626373626</v>
+        <v>-30</v>
       </c>
       <c r="L16" s="15">
-        <v>-40.707964601769</v>
+        <v>-44</v>
       </c>
       <c r="M16" s="15">
-        <v>-12.987012987013</v>
+        <v>-15.662650602409</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.364864864864</v>
+        <v>-77.777777777777</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>6.666666666666</v>
+        <v>18.181818181818</v>
       </c>
       <c r="F17" s="14">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G17" s="14">
         <v>51</v>
       </c>
       <c r="H17" s="15">
-        <v>-3.921568627450</v>
+        <v>5.882352941176</v>
       </c>
       <c r="I17" s="14">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="J17" s="14">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="K17" s="15">
-        <v>-19.428571428571</v>
+        <v>-17.204301075268</v>
       </c>
       <c r="L17" s="15">
-        <v>-7.236842105263</v>
+        <v>-10.982658959537</v>
       </c>
       <c r="M17" s="15">
-        <v>80.769230769230</v>
+        <v>87.804878048780</v>
       </c>
       <c r="N17" s="15">
-        <v>5.223880597014</v>
+        <v>1.986754966887</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H18" s="15">
-        <v>-5.263157894736</v>
+        <v>10</v>
       </c>
       <c r="I18" s="14">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J18" s="14">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K18" s="15">
-        <v>25.757575757575</v>
+        <v>23.943661971831</v>
       </c>
       <c r="L18" s="15">
-        <v>16.901408450704</v>
+        <v>20.547945205479</v>
       </c>
       <c r="M18" s="15">
-        <v>72.916666666666</v>
+        <v>66.037735849056</v>
       </c>
       <c r="N18" s="15">
-        <v>-75.872093023255</v>
+        <v>-76.021798365122</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>-27.272727272727</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G19" s="14">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H19" s="15">
-        <v>-9.090909090909</v>
+        <v>-6.25</v>
       </c>
       <c r="I19" s="14">
+        <v>161</v>
+      </c>
+      <c r="J19" s="14">
         <v>152</v>
       </c>
-      <c r="J19" s="14">
-        <v>143</v>
-      </c>
       <c r="K19" s="15">
-        <v>6.293706293706</v>
+        <v>5.921052631578</v>
       </c>
       <c r="L19" s="15">
-        <v>-2.564102564102</v>
+        <v>-3.592814371257</v>
       </c>
       <c r="M19" s="15">
-        <v>153.333333333333</v>
+        <v>147.692307692308</v>
       </c>
       <c r="N19" s="15">
-        <v>38.181818181818</v>
+        <v>35.294117647058</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>42.857142857142</v>
+        <v>50</v>
       </c>
       <c r="F20" s="14">
         <v>23</v>
       </c>
       <c r="G20" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H20" s="15">
-        <v>43.75</v>
+        <v>53.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="J20" s="14">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>3.703703703703</v>
       </c>
       <c r="L20" s="15">
-        <v>-5.454545454545</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="M20" s="15">
-        <v>147.619047619048</v>
+        <v>143.478260869565</v>
       </c>
       <c r="N20" s="15">
-        <v>-65.100671140939</v>
+        <v>-64.556962025316</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D21" s="17">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="F21" s="17">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G21" s="17">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.592814371257</v>
+        <v>-2.958579881656</v>
       </c>
       <c r="I21" s="17">
-        <v>504</v>
+        <v>538</v>
       </c>
       <c r="J21" s="17">
-        <v>536</v>
+        <v>576</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.970149253731</v>
+        <v>-6.597222222222</v>
       </c>
       <c r="L21" s="18">
-        <v>-8.860759493670</v>
+        <v>-10.927152317880</v>
       </c>
       <c r="M21" s="18">
-        <v>73.793103448275</v>
+        <v>71.884984025559</v>
       </c>
       <c r="N21" s="18">
-        <v>-52.136752136752</v>
+        <v>-52.557319223985</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,11 +1191,11 @@
       <c r="F22" s="14">
         <v>1</v>
       </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>0</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>50</v>
       </c>
       <c r="L22" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
         <v>200</v>
@@ -1230,7 +1230,7 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>20</v>
@@ -1239,19 +1239,19 @@
         <v>21</v>
       </c>
       <c r="I23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J23" s="14">
         <v>1</v>
       </c>
       <c r="K23" s="15">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="L23" s="15">
-        <v>-28.571428571428</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M23" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>-14.285714285714</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="F24" s="14">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="G24" s="14">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H24" s="15">
-        <v>-14.159292035398</v>
+        <v>-25.217391304347</v>
       </c>
       <c r="I24" s="14">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="J24" s="14">
-        <v>321</v>
+        <v>347</v>
       </c>
       <c r="K24" s="15">
-        <v>-12.461059190031</v>
+        <v>-14.985590778098</v>
       </c>
       <c r="L24" s="15">
-        <v>8.076923076923</v>
+        <v>4.609929078014</v>
       </c>
       <c r="M24" s="15">
-        <v>43.367346938775</v>
+        <v>38.497652582159</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
-      </c>
-      <c r="D25" s="14">
-        <v>7</v>
-      </c>
-      <c r="E25" s="15">
-        <v>-42.857142857142</v>
+        <v>5</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F25" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G25" s="14">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H25" s="15">
-        <v>-29.166666666666</v>
+        <v>-20</v>
       </c>
       <c r="I25" s="14">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J25" s="14">
         <v>82</v>
       </c>
       <c r="K25" s="15">
-        <v>-32.926829268292</v>
+        <v>-26.829268292682</v>
       </c>
       <c r="L25" s="15">
-        <v>-12.698412698412</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D26" s="14">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="E26" s="15">
-        <v>56.25</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G26" s="14">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="H26" s="15">
-        <v>6.329113924050</v>
+        <v>-15.957446808510</v>
       </c>
       <c r="I26" s="14">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="J26" s="14">
-        <v>203</v>
+        <v>239</v>
       </c>
       <c r="K26" s="15">
-        <v>2.955665024630</v>
+        <v>-7.112970711297</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.415094339622</v>
+        <v>-3.056768558951</v>
       </c>
       <c r="M26" s="15">
-        <v>7.179487179487</v>
+        <v>7.766990291262</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
-      </c>
-      <c r="D27" s="13" t="s">
+      <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>3</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>50</v>
+        <v>-40</v>
       </c>
       <c r="I27" s="14">
         <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>11.111111111111</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>3</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
         <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>-30</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J28" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K28" s="15">
-        <v>-13.043478260869</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="L28" s="15">
-        <v>25</v>
+        <v>10.526315789473</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,38 +1469,38 @@
       <c r="C29" s="14">
         <v>2</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>100</v>
       </c>
       <c r="F29" s="14">
         <v>4</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>300</v>
       </c>
       <c r="I29" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J29" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M29" s="15">
-        <v>-58.333333333333</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-77.272727272727</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,40 +1508,40 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
+        <v>2</v>
+      </c>
+      <c r="D30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="E30" s="15">
+        <v>100</v>
       </c>
       <c r="F30" s="14">
         <v>3</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>200</v>
       </c>
       <c r="I30" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J30" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K30" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="N30" s="15">
-        <v>-80.952380952380</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-048pct.xlsx
+++ b/data/source/weekly/cs-en-us-048pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
-        <v>3</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
         <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J15" s="14">
         <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>-11.111111111111</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L15" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>14.285714285714</v>
+        <v>42.857142857142</v>
       </c>
       <c r="N15" s="15">
-        <v>-27.272727272727</v>
+        <v>-28.571428571428</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E16" s="15">
-        <v>-55.555555555555</v>
+        <v>-68.75</v>
       </c>
       <c r="F16" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G16" s="14">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="H16" s="15">
-        <v>-43.333333333333</v>
+        <v>-52.380952380952</v>
       </c>
       <c r="I16" s="14">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J16" s="14">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="K16" s="15">
-        <v>-30</v>
+        <v>-35.344827586206</v>
       </c>
       <c r="L16" s="15">
-        <v>-44</v>
+        <v>-45.652173913043</v>
       </c>
       <c r="M16" s="15">
-        <v>-15.662650602409</v>
+        <v>-15.730337078651</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.777777777777</v>
+        <v>-77.272727272727</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E17" s="15">
-        <v>18.181818181818</v>
+        <v>-80</v>
       </c>
       <c r="F17" s="14">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G17" s="14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H17" s="15">
-        <v>5.882352941176</v>
+        <v>-16.363636363636</v>
       </c>
       <c r="I17" s="14">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="J17" s="14">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="K17" s="15">
-        <v>-17.204301075268</v>
+        <v>-22.815533980582</v>
       </c>
       <c r="L17" s="15">
-        <v>-10.982658959537</v>
+        <v>-10.674157303370</v>
       </c>
       <c r="M17" s="15">
-        <v>87.804878048780</v>
+        <v>89.285714285714</v>
       </c>
       <c r="N17" s="15">
-        <v>1.986754966887</v>
+        <v>-1.851851851851</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,13 +1016,13 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14">
         <v>22</v>
@@ -1034,22 +1034,22 @@
         <v>10</v>
       </c>
       <c r="I18" s="14">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="J18" s="14">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K18" s="15">
-        <v>23.943661971831</v>
+        <v>25.333333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>20.547945205479</v>
+        <v>18.987341772151</v>
       </c>
       <c r="M18" s="15">
-        <v>66.037735849056</v>
+        <v>64.912280701754</v>
       </c>
       <c r="N18" s="15">
-        <v>-76.021798365122</v>
+        <v>-75.647668393782</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F19" s="14">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G19" s="14">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H19" s="15">
-        <v>-6.25</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="I19" s="14">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="J19" s="14">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="K19" s="15">
-        <v>5.921052631578</v>
+        <v>4.320987654320</v>
       </c>
       <c r="L19" s="15">
-        <v>-3.592814371257</v>
+        <v>-4.519774011299</v>
       </c>
       <c r="M19" s="15">
-        <v>147.692307692308</v>
+        <v>131.506849315069</v>
       </c>
       <c r="N19" s="15">
-        <v>35.294117647058</v>
+        <v>34.126984126984</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G20" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H20" s="15">
-        <v>53.333333333333</v>
+        <v>29.411764705882</v>
       </c>
       <c r="I20" s="14">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J20" s="14">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K20" s="15">
-        <v>3.703703703703</v>
+        <v>-1.666666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-3.448275862068</v>
+        <v>-9.230769230769</v>
       </c>
       <c r="M20" s="15">
-        <v>143.478260869565</v>
+        <v>145.833333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-64.556962025316</v>
+        <v>-65.497076023391</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="E21" s="18">
-        <v>-15</v>
+        <v>-50</v>
       </c>
       <c r="F21" s="17">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G21" s="17">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.958579881656</v>
+        <v>-14.594594594594</v>
       </c>
       <c r="I21" s="17">
-        <v>538</v>
+        <v>567</v>
       </c>
       <c r="J21" s="17">
-        <v>576</v>
+        <v>632</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.597222222222</v>
+        <v>-10.284810126582</v>
       </c>
       <c r="L21" s="18">
-        <v>-10.927152317880</v>
+        <v>-12.093023255814</v>
       </c>
       <c r="M21" s="18">
-        <v>71.884984025559</v>
+        <v>69.760479041916</v>
       </c>
       <c r="N21" s="18">
-        <v>-52.557319223985</v>
+        <v>-52.828618968386</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,8 +1188,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="14">
-        <v>1</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E24" s="15">
-        <v>-42.307692307692</v>
+        <v>-48.571428571428</v>
       </c>
       <c r="F24" s="14">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G24" s="14">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="H24" s="15">
-        <v>-25.217391304347</v>
+        <v>-31.147540983606</v>
       </c>
       <c r="I24" s="14">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="J24" s="14">
-        <v>347</v>
+        <v>382</v>
       </c>
       <c r="K24" s="15">
-        <v>-14.985590778098</v>
+        <v>-18.062827225130</v>
       </c>
       <c r="L24" s="15">
-        <v>4.609929078014</v>
+        <v>5.033557046979</v>
       </c>
       <c r="M24" s="15">
-        <v>38.497652582159</v>
+        <v>32.067510548523</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,13 +1303,13 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="D25" s="14">
+        <v>4</v>
+      </c>
+      <c r="E25" s="15">
+        <v>0</v>
       </c>
       <c r="F25" s="14">
         <v>16</v>
@@ -1321,16 +1321,16 @@
         <v>-20</v>
       </c>
       <c r="I25" s="14">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J25" s="14">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K25" s="15">
-        <v>-26.829268292682</v>
+        <v>-25.581395348837</v>
       </c>
       <c r="L25" s="15">
-        <v>-9.090909090909</v>
+        <v>-7.246376811594</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D26" s="14">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E26" s="15">
-        <v>-58.333333333333</v>
+        <v>-29.629629629629</v>
       </c>
       <c r="F26" s="14">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G26" s="14">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="H26" s="15">
-        <v>-15.957446808510</v>
+        <v>-21.568627450980</v>
       </c>
       <c r="I26" s="14">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="J26" s="14">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="K26" s="15">
-        <v>-7.112970711297</v>
+        <v>-9.398496240601</v>
       </c>
       <c r="L26" s="15">
-        <v>-3.056768558951</v>
+        <v>-0.823045267489</v>
       </c>
       <c r="M26" s="15">
-        <v>7.766990291262</v>
+        <v>6.167400881057</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="14">
-        <v>3</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="C27" s="14">
+        <v>2</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
         <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="I27" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J27" s="14">
         <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
-        <v>3</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-66.666666666666</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J28" s="14">
         <v>26</v>
       </c>
       <c r="K28" s="15">
-        <v>-19.230769230769</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="L28" s="15">
-        <v>10.526315789473</v>
+        <v>15</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1467,40 +1467,40 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" s="14">
         <v>1</v>
       </c>
       <c r="E29" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="I29" s="14">
+        <v>8</v>
+      </c>
+      <c r="J29" s="14">
         <v>7</v>
       </c>
-      <c r="J29" s="14">
-        <v>6</v>
-      </c>
       <c r="K29" s="15">
-        <v>16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L29" s="15">
-        <v>16.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>-41.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-75</v>
+        <v>-71.428571428571</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,40 +1508,40 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="14">
         <v>1</v>
       </c>
       <c r="E30" s="15">
+        <v>0</v>
+      </c>
+      <c r="F30" s="14">
+        <v>4</v>
+      </c>
+      <c r="G30" s="14">
+        <v>2</v>
+      </c>
+      <c r="H30" s="15">
         <v>100</v>
       </c>
-      <c r="F30" s="14">
-        <v>3</v>
-      </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>200</v>
-      </c>
       <c r="I30" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J30" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K30" s="15">
         <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>-40</v>
+        <v>-30</v>
       </c>
       <c r="N30" s="15">
-        <v>-75</v>
+        <v>-70.833333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-048pct.xlsx
+++ b/data/source/weekly/cs-en-us-048pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -854,17 +854,17 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>2</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -873,10 +873,10 @@
         <v>1</v>
       </c>
       <c r="J14" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K14" s="15">
-        <v>-75</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="L14" s="15">
         <v>-50</v>
@@ -892,14 +892,14 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>4</v>
@@ -914,10 +914,10 @@
         <v>10</v>
       </c>
       <c r="J15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
         <v>66.666666666666</v>
@@ -926,7 +926,7 @@
         <v>42.857142857142</v>
       </c>
       <c r="N15" s="15">
-        <v>-28.571428571428</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D16" s="14">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E16" s="15">
-        <v>-68.75</v>
+        <v>-12.5</v>
       </c>
       <c r="F16" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G16" s="14">
         <v>42</v>
       </c>
       <c r="H16" s="15">
-        <v>-52.380952380952</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="I16" s="14">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="J16" s="14">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="K16" s="15">
-        <v>-35.344827586206</v>
+        <v>-33.870967741935</v>
       </c>
       <c r="L16" s="15">
-        <v>-45.652173913043</v>
+        <v>-44.217687074829</v>
       </c>
       <c r="M16" s="15">
-        <v>-15.730337078651</v>
+        <v>-15.463917525773</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.272727272727</v>
+        <v>-76.368876080691</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D17" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E17" s="15">
-        <v>-80</v>
+        <v>-6.25</v>
       </c>
       <c r="F17" s="14">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G17" s="14">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H17" s="15">
-        <v>-16.363636363636</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="I17" s="14">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="J17" s="14">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="K17" s="15">
-        <v>-22.815533980582</v>
+        <v>-20.270270270270</v>
       </c>
       <c r="L17" s="15">
-        <v>-10.674157303370</v>
+        <v>-6.842105263157</v>
       </c>
       <c r="M17" s="15">
-        <v>89.285714285714</v>
+        <v>94.505494505494</v>
       </c>
       <c r="N17" s="15">
-        <v>-1.851851851851</v>
+        <v>2.312138728323</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="F18" s="14">
         <v>22</v>
       </c>
       <c r="G18" s="14">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H18" s="15">
+        <v>-18.518518518518</v>
+      </c>
+      <c r="I18" s="14">
+        <v>99</v>
+      </c>
+      <c r="J18" s="14">
+        <v>86</v>
+      </c>
+      <c r="K18" s="15">
+        <v>15.116279069767</v>
+      </c>
+      <c r="L18" s="15">
         <v>10</v>
       </c>
-      <c r="I18" s="14">
-        <v>94</v>
-      </c>
-      <c r="J18" s="14">
-        <v>75</v>
-      </c>
-      <c r="K18" s="15">
-        <v>25.333333333333</v>
-      </c>
-      <c r="L18" s="15">
-        <v>18.987341772151</v>
-      </c>
       <c r="M18" s="15">
-        <v>64.912280701754</v>
+        <v>59.677419354838</v>
       </c>
       <c r="N18" s="15">
-        <v>-75.647668393782</v>
+        <v>-75.434243176178</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E19" s="15">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
       <c r="F19" s="14">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G19" s="14">
         <v>46</v>
       </c>
       <c r="H19" s="15">
-        <v>-4.347826086956</v>
+        <v>-15.217391304347</v>
       </c>
       <c r="I19" s="14">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="J19" s="14">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="K19" s="15">
-        <v>4.320987654320</v>
+        <v>2.808988764044</v>
       </c>
       <c r="L19" s="15">
-        <v>-4.519774011299</v>
+        <v>-3.174603174603</v>
       </c>
       <c r="M19" s="15">
-        <v>131.506849315069</v>
+        <v>131.645569620253</v>
       </c>
       <c r="N19" s="15">
-        <v>34.126984126984</v>
+        <v>32.608695652173</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>-62.5</v>
       </c>
       <c r="F20" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G20" s="14">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H20" s="15">
-        <v>29.411764705882</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="I20" s="14">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J20" s="14">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="K20" s="15">
-        <v>-1.666666666666</v>
+        <v>-7.352941176470</v>
       </c>
       <c r="L20" s="15">
-        <v>-9.230769230769</v>
+        <v>-11.267605633802</v>
       </c>
       <c r="M20" s="15">
-        <v>145.833333333333</v>
+        <v>142.307692307692</v>
       </c>
       <c r="N20" s="15">
-        <v>-65.497076023391</v>
+        <v>-65</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D21" s="17">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E21" s="18">
-        <v>-50</v>
+        <v>-29.032258064516</v>
       </c>
       <c r="F21" s="17">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G21" s="17">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="H21" s="18">
-        <v>-14.594594594594</v>
+        <v>-24.154589371980</v>
       </c>
       <c r="I21" s="17">
-        <v>567</v>
+        <v>615</v>
       </c>
       <c r="J21" s="17">
-        <v>632</v>
+        <v>694</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.284810126582</v>
+        <v>-11.383285302593</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.093023255814</v>
+        <v>-11.510791366906</v>
       </c>
       <c r="M21" s="18">
-        <v>69.760479041916</v>
+        <v>69.889502762430</v>
       </c>
       <c r="N21" s="18">
-        <v>-52.828618968386</v>
+        <v>-51.536643026004</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1230,7 +1230,7 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>20</v>
@@ -1239,19 +1239,19 @@
         <v>21</v>
       </c>
       <c r="I23" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J23" s="14">
         <v>1</v>
       </c>
       <c r="K23" s="15">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="L23" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="M23" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>-48.571428571428</v>
+        <v>36.842105263157</v>
       </c>
       <c r="F24" s="14">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G24" s="14">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="H24" s="15">
-        <v>-31.147540983606</v>
+        <v>-24.074074074074</v>
       </c>
       <c r="I24" s="14">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="J24" s="14">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="K24" s="15">
-        <v>-18.062827225130</v>
+        <v>-15.710723192019</v>
       </c>
       <c r="L24" s="15">
-        <v>5.033557046979</v>
+        <v>6.624605678233</v>
       </c>
       <c r="M24" s="15">
-        <v>32.067510548523</v>
+        <v>32.549019607843</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F25" s="14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G25" s="14">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H25" s="15">
-        <v>-20</v>
+        <v>50</v>
       </c>
       <c r="I25" s="14">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="J25" s="14">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K25" s="15">
-        <v>-25.581395348837</v>
+        <v>-19.101123595505</v>
       </c>
       <c r="L25" s="15">
-        <v>-7.246376811594</v>
+        <v>-4</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D26" s="14">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E26" s="15">
-        <v>-29.629629629629</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G26" s="14">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H26" s="15">
-        <v>-21.568627450980</v>
+        <v>-18.556701030927</v>
       </c>
       <c r="I26" s="14">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="J26" s="14">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="K26" s="15">
-        <v>-9.398496240601</v>
+        <v>-7.746478873239</v>
       </c>
       <c r="L26" s="15">
-        <v>-0.823045267489</v>
+        <v>1.550387596899</v>
       </c>
       <c r="M26" s="15">
-        <v>6.167400881057</v>
+        <v>7.377049180327</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>4</v>
       </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>12</v>
       </c>
       <c r="J27" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K27" s="15">
+        <v>-7.692307692307</v>
+      </c>
+      <c r="L27" s="15">
         <v>0</v>
-      </c>
-      <c r="L27" s="15">
-        <v>9.090909090909</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1438,22 +1438,22 @@
         <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J28" s="14">
         <v>26</v>
       </c>
       <c r="K28" s="15">
-        <v>-11.538461538461</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="L28" s="15">
-        <v>15</v>
+        <v>8.695652173913</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,32 +1466,32 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>5</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H29" s="15">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="I29" s="14">
         <v>8</v>
       </c>
       <c r="J29" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K29" s="15">
-        <v>14.285714285714</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L29" s="15">
         <v>33.333333333333</v>
@@ -1500,39 +1500,39 @@
         <v>-33.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-71.428571428571</v>
+        <v>-73.333333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>4</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H30" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
         <v>7</v>
       </c>
       <c r="J30" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L30" s="15">
         <v>16.666666666666</v>
@@ -1541,7 +1541,7 @@
         <v>-30</v>
       </c>
       <c r="N30" s="15">
-        <v>-70.833333333333</v>
+        <v>-73.076923076923</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-048pct.xlsx
+++ b/data/source/weekly/cs-en-us-048pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>2</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -885,7 +885,7 @@
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>-92.307692307692</v>
+        <v>-93.75</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -902,31 +902,31 @@
         <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="I15" s="14">
         <v>10</v>
       </c>
       <c r="J15" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L15" s="15">
         <v>66.666666666666</v>
       </c>
       <c r="M15" s="15">
-        <v>42.857142857142</v>
+        <v>25</v>
       </c>
       <c r="N15" s="15">
-        <v>-33.333333333333</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>-12.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
         <v>22</v>
@@ -952,22 +952,22 @@
         <v>-47.619047619047</v>
       </c>
       <c r="I16" s="14">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="J16" s="14">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="K16" s="15">
-        <v>-33.870967741935</v>
+        <v>-33.834586466165</v>
       </c>
       <c r="L16" s="15">
-        <v>-44.217687074829</v>
+        <v>-43.589743589743</v>
       </c>
       <c r="M16" s="15">
-        <v>-15.463917525773</v>
+        <v>-16.190476190476</v>
       </c>
       <c r="N16" s="15">
-        <v>-76.368876080691</v>
+        <v>-76.216216216216</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D17" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15">
-        <v>-6.25</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G17" s="14">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H17" s="15">
-        <v>-19.354838709677</v>
+        <v>-20.338983050847</v>
       </c>
       <c r="I17" s="14">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="J17" s="14">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="K17" s="15">
-        <v>-20.270270270270</v>
+        <v>-18.803418803418</v>
       </c>
       <c r="L17" s="15">
-        <v>-6.842105263157</v>
+        <v>-7.317073170731</v>
       </c>
       <c r="M17" s="15">
-        <v>94.505494505494</v>
+        <v>93.877551020408</v>
       </c>
       <c r="N17" s="15">
-        <v>2.312138728323</v>
+        <v>1.604278074866</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-54.545454545454</v>
+        <v>-25</v>
       </c>
       <c r="F18" s="14">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H18" s="15">
-        <v>-18.518518518518</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J18" s="14">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="K18" s="15">
-        <v>15.116279069767</v>
+        <v>12.222222222222</v>
       </c>
       <c r="L18" s="15">
-        <v>10</v>
+        <v>6.315789473684</v>
       </c>
       <c r="M18" s="15">
-        <v>59.677419354838</v>
+        <v>55.384615384615</v>
       </c>
       <c r="N18" s="15">
-        <v>-75.434243176178</v>
+        <v>-75.952380952380</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D19" s="14">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>-12.5</v>
+        <v>125</v>
       </c>
       <c r="F19" s="14">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G19" s="14">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H19" s="15">
-        <v>-15.217391304347</v>
+        <v>16.279069767441</v>
       </c>
       <c r="I19" s="14">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="J19" s="14">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="K19" s="15">
-        <v>2.808988764044</v>
+        <v>8.602150537634</v>
       </c>
       <c r="L19" s="15">
-        <v>-3.174603174603</v>
+        <v>1.507537688442</v>
       </c>
       <c r="M19" s="15">
-        <v>131.645569620253</v>
+        <v>129.545454545455</v>
       </c>
       <c r="N19" s="15">
-        <v>32.608695652173</v>
+        <v>39.310344827586</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>-62.5</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F20" s="14">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G20" s="14">
         <v>23</v>
       </c>
       <c r="H20" s="15">
-        <v>-13.043478260869</v>
+        <v>-52.173913043478</v>
       </c>
       <c r="I20" s="14">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J20" s="14">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K20" s="15">
-        <v>-7.352941176470</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-11.267605633802</v>
+        <v>-17.721518987341</v>
       </c>
       <c r="M20" s="15">
-        <v>142.307692307692</v>
+        <v>116.666666666667</v>
       </c>
       <c r="N20" s="15">
-        <v>-65</v>
+        <v>-65.968586387434</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D21" s="17">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E21" s="18">
-        <v>-29.032258064516</v>
+        <v>2.439024390243</v>
       </c>
       <c r="F21" s="17">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="G21" s="17">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="H21" s="18">
-        <v>-24.154589371980</v>
+        <v>-25.125628140703</v>
       </c>
       <c r="I21" s="17">
-        <v>615</v>
+        <v>657</v>
       </c>
       <c r="J21" s="17">
-        <v>694</v>
+        <v>735</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.383285302593</v>
+        <v>-10.612244897959</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.510791366906</v>
+        <v>-11.455525606469</v>
       </c>
       <c r="M21" s="18">
-        <v>69.889502762430</v>
+        <v>66.751269035533</v>
       </c>
       <c r="N21" s="18">
-        <v>-51.536643026004</v>
+        <v>-51.152416356877</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1230,7 +1230,7 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>20</v>
@@ -1248,10 +1248,10 @@
         <v>600</v>
       </c>
       <c r="L23" s="15">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="M23" s="15">
-        <v>133.333333333333</v>
+        <v>75</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E24" s="15">
-        <v>36.842105263157</v>
+        <v>37.5</v>
       </c>
       <c r="F24" s="14">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G24" s="14">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="H24" s="15">
-        <v>-24.074074074074</v>
+        <v>-15.625</v>
       </c>
       <c r="I24" s="14">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="J24" s="14">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="K24" s="15">
-        <v>-15.710723192019</v>
+        <v>-13.908872901678</v>
       </c>
       <c r="L24" s="15">
-        <v>6.624605678233</v>
+        <v>4.057971014492</v>
       </c>
       <c r="M24" s="15">
-        <v>32.549019607843</v>
+        <v>33.457249070632</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
         <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>200</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G25" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H25" s="15">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="I25" s="14">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J25" s="14">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K25" s="15">
-        <v>-19.101123595505</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="L25" s="15">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E26" s="15">
-        <v>16.666666666666</v>
+        <v>-47.826086956521</v>
       </c>
       <c r="F26" s="14">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="G26" s="14">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="H26" s="15">
-        <v>-18.556701030927</v>
+        <v>-35.576923076923</v>
       </c>
       <c r="I26" s="14">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="J26" s="14">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="K26" s="15">
-        <v>-7.746478873239</v>
+        <v>-10.749185667752</v>
       </c>
       <c r="L26" s="15">
-        <v>1.550387596899</v>
+        <v>-1.792114695340</v>
       </c>
       <c r="M26" s="15">
-        <v>7.377049180327</v>
+        <v>4.580152671755</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,31 +1388,31 @@
         <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
         <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="14">
         <v>12</v>
       </c>
       <c r="J27" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K27" s="15">
-        <v>-7.692307692307</v>
+        <v>-20</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>5</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-80</v>
       </c>
       <c r="F28" s="14">
         <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J28" s="14">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K28" s="15">
-        <v>-3.846153846153</v>
+        <v>-16.129032258064</v>
       </c>
       <c r="L28" s="15">
-        <v>8.695652173913</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,55 +1466,55 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="14">
-        <v>2</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G29" s="14">
         <v>4</v>
       </c>
       <c r="H29" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J29" s="14">
         <v>9</v>
       </c>
       <c r="K29" s="15">
-        <v>-11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>33.333333333333</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M29" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="N29" s="15">
-        <v>-73.333333333333</v>
+        <v>-70.967741935483</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="14">
-        <v>2</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>4</v>
@@ -1526,22 +1526,22 @@
         <v>0</v>
       </c>
       <c r="I30" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J30" s="14">
         <v>9</v>
       </c>
       <c r="K30" s="15">
-        <v>-22.222222222222</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L30" s="15">
-        <v>16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M30" s="15">
-        <v>-30</v>
+        <v>-20</v>
       </c>
       <c r="N30" s="15">
-        <v>-73.076923076923</v>
+        <v>-70.370370370370</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-048pct.xlsx
+++ b/data/source/weekly/cs-en-us-048pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -873,10 +873,10 @@
         <v>1</v>
       </c>
       <c r="J14" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K14" s="15">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="L14" s="15">
         <v>-50</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="14">
+        <v>3</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
+        <v>5</v>
+      </c>
+      <c r="G15" s="14">
         <v>2</v>
       </c>
-      <c r="G15" s="14">
-        <v>5</v>
-      </c>
       <c r="H15" s="15">
-        <v>-60</v>
+        <v>150</v>
       </c>
       <c r="I15" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J15" s="14">
         <v>11</v>
       </c>
       <c r="K15" s="15">
-        <v>-9.090909090909</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L15" s="15">
-        <v>66.666666666666</v>
+        <v>85.714285714285</v>
       </c>
       <c r="M15" s="15">
-        <v>25</v>
+        <v>62.5</v>
       </c>
       <c r="N15" s="15">
-        <v>-37.5</v>
+        <v>-31.578947368421</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -943,31 +943,31 @@
         <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G16" s="14">
         <v>42</v>
       </c>
       <c r="H16" s="15">
-        <v>-47.619047619047</v>
+        <v>-40.476190476190</v>
       </c>
       <c r="I16" s="14">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="J16" s="14">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="K16" s="15">
-        <v>-33.834586466165</v>
+        <v>-33.098591549295</v>
       </c>
       <c r="L16" s="15">
-        <v>-43.589743589743</v>
+        <v>-41.358024691358</v>
       </c>
       <c r="M16" s="15">
-        <v>-16.190476190476</v>
+        <v>-12.844036697247</v>
       </c>
       <c r="N16" s="15">
-        <v>-76.216216216216</v>
+        <v>-75.765306122449</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" s="14">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E17" s="15">
-        <v>8.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
         <v>47</v>
       </c>
       <c r="G17" s="14">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="H17" s="15">
-        <v>-20.338983050847</v>
+        <v>-31.884057971014</v>
       </c>
       <c r="I17" s="14">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="J17" s="14">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="K17" s="15">
-        <v>-18.803418803418</v>
+        <v>-20</v>
       </c>
       <c r="L17" s="15">
-        <v>-7.317073170731</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="M17" s="15">
-        <v>93.877551020408</v>
+        <v>94.285714285714</v>
       </c>
       <c r="N17" s="15">
-        <v>1.604278074866</v>
+        <v>1.492537313432</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G18" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H18" s="15">
-        <v>-29.166666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I18" s="14">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J18" s="14">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K18" s="15">
-        <v>12.222222222222</v>
+        <v>11.956521739130</v>
       </c>
       <c r="L18" s="15">
-        <v>6.315789473684</v>
+        <v>0</v>
       </c>
       <c r="M18" s="15">
-        <v>55.384615384615</v>
+        <v>53.731343283582</v>
       </c>
       <c r="N18" s="15">
-        <v>-75.952380952380</v>
+        <v>-77.008928571428</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E19" s="15">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="G19" s="14">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="H19" s="15">
-        <v>16.279069767441</v>
+        <v>11.320754716981</v>
       </c>
       <c r="I19" s="14">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="J19" s="14">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="K19" s="15">
-        <v>8.602150537634</v>
+        <v>7.804878048780</v>
       </c>
       <c r="L19" s="15">
-        <v>1.507537688442</v>
+        <v>6.25</v>
       </c>
       <c r="M19" s="15">
-        <v>129.545454545455</v>
+        <v>132.631578947368</v>
       </c>
       <c r="N19" s="15">
-        <v>39.310344827586</v>
+        <v>46.357615894039</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>-71.428571428571</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
         <v>11</v>
       </c>
       <c r="G20" s="14">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H20" s="15">
-        <v>-52.173913043478</v>
+        <v>-63.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J20" s="14">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="K20" s="15">
-        <v>-13.333333333333</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="L20" s="15">
-        <v>-17.721518987341</v>
+        <v>-20</v>
       </c>
       <c r="M20" s="15">
-        <v>116.666666666667</v>
+        <v>94.285714285714</v>
       </c>
       <c r="N20" s="15">
-        <v>-65.968586387434</v>
+        <v>-66</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D21" s="17">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="E21" s="18">
-        <v>2.439024390243</v>
+        <v>-22.950819672131</v>
       </c>
       <c r="F21" s="17">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="G21" s="17">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="H21" s="18">
-        <v>-25.125628140703</v>
+        <v>-26.363636363636</v>
       </c>
       <c r="I21" s="17">
-        <v>657</v>
+        <v>705</v>
       </c>
       <c r="J21" s="17">
-        <v>735</v>
+        <v>796</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.612244897959</v>
+        <v>-11.432160804020</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.455525606469</v>
+        <v>-9.961685823754</v>
       </c>
       <c r="M21" s="18">
-        <v>66.751269035533</v>
+        <v>68.257756563245</v>
       </c>
       <c r="N21" s="18">
-        <v>-51.152416356877</v>
+        <v>-50.595655220742</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1188,8 +1188,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="14">
         <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="C23" s="14">
+        <v>2</v>
+      </c>
+      <c r="D23" s="14">
+        <v>2</v>
+      </c>
+      <c r="E23" s="15">
+        <v>0</v>
       </c>
       <c r="F23" s="14">
         <v>2</v>
       </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
+      <c r="G23" s="14">
+        <v>2</v>
+      </c>
+      <c r="H23" s="15">
+        <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K23" s="15">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="L23" s="15">
-        <v>-12.5</v>
+        <v>12.5</v>
       </c>
       <c r="M23" s="15">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D24" s="14">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E24" s="15">
-        <v>37.5</v>
+        <v>240</v>
       </c>
       <c r="F24" s="14">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="G24" s="14">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="H24" s="15">
-        <v>-15.625</v>
+        <v>23.75</v>
       </c>
       <c r="I24" s="14">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="J24" s="14">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="K24" s="15">
-        <v>-13.908872901678</v>
+        <v>-8.196721311475</v>
       </c>
       <c r="L24" s="15">
-        <v>4.057971014492</v>
+        <v>8.888888888888</v>
       </c>
       <c r="M24" s="15">
-        <v>33.457249070632</v>
+        <v>39.501779359430</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
         <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F25" s="14">
         <v>22</v>
       </c>
       <c r="G25" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H25" s="15">
-        <v>120</v>
+        <v>69.230769230769</v>
       </c>
       <c r="I25" s="14">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J25" s="14">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K25" s="15">
-        <v>-17.391304347826</v>
+        <v>-14.736842105263</v>
       </c>
       <c r="L25" s="15">
-        <v>-5</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="D26" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E26" s="15">
-        <v>-47.826086956521</v>
+        <v>16</v>
       </c>
       <c r="F26" s="14">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="G26" s="14">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="H26" s="15">
-        <v>-35.576923076923</v>
+        <v>-11.827956989247</v>
       </c>
       <c r="I26" s="14">
-        <v>274</v>
+        <v>303</v>
       </c>
       <c r="J26" s="14">
-        <v>307</v>
+        <v>332</v>
       </c>
       <c r="K26" s="15">
-        <v>-10.749185667752</v>
+        <v>-8.734939759036</v>
       </c>
       <c r="L26" s="15">
-        <v>-1.792114695340</v>
+        <v>3.412969283276</v>
       </c>
       <c r="M26" s="15">
-        <v>4.580152671755</v>
+        <v>8.602150537634</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>3</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="I27" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J27" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K27" s="15">
-        <v>-20</v>
+        <v>-6.25</v>
       </c>
       <c r="L27" s="15">
-        <v>-14.285714285714</v>
+        <v>-6.25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-80</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
         <v>6</v>
       </c>
       <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="15">
+        <v>-14.285714285714</v>
+      </c>
+      <c r="I28" s="14">
+        <v>27</v>
+      </c>
+      <c r="J28" s="14">
+        <v>33</v>
+      </c>
+      <c r="K28" s="15">
+        <v>-18.181818181818</v>
+      </c>
+      <c r="L28" s="15">
         <v>8</v>
-      </c>
-      <c r="H28" s="15">
-        <v>-25</v>
-      </c>
-      <c r="I28" s="14">
-        <v>26</v>
-      </c>
-      <c r="J28" s="14">
-        <v>31</v>
-      </c>
-      <c r="K28" s="15">
-        <v>-16.129032258064</v>
-      </c>
-      <c r="L28" s="15">
-        <v>8.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,32 +1466,32 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
-      </c>
-      <c r="D29" s="13" t="s">
+      <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>2</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="I29" s="14">
         <v>9</v>
       </c>
       <c r="J29" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L29" s="15">
         <v>28.571428571428</v>
@@ -1500,39 +1500,39 @@
         <v>-25</v>
       </c>
       <c r="N29" s="15">
-        <v>-70.967741935483</v>
+        <v>-71.875</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
-      </c>
-      <c r="D30" s="13" t="s">
+      <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>2</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="I30" s="14">
         <v>8</v>
       </c>
       <c r="J30" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K30" s="15">
-        <v>-11.111111111111</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L30" s="15">
         <v>14.285714285714</v>
@@ -1541,7 +1541,7 @@
         <v>-20</v>
       </c>
       <c r="N30" s="15">
-        <v>-70.370370370370</v>
+        <v>-71.428571428571</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-048pct.xlsx
+++ b/data/source/weekly/cs-en-us-048pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -879,45 +879,45 @@
         <v>-85.714285714285</v>
       </c>
       <c r="L14" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>-93.75</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="14">
         <v>3</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <v>5</v>
-      </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>13</v>
       </c>
       <c r="J15" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K15" s="15">
-        <v>18.181818181818</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L15" s="15">
         <v>85.714285714285</v>
@@ -926,7 +926,7 @@
         <v>62.5</v>
       </c>
       <c r="N15" s="15">
-        <v>-31.578947368421</v>
+        <v>-40.909090909090</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
         <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="F16" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G16" s="14">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H16" s="15">
-        <v>-40.476190476190</v>
+        <v>-37.142857142857</v>
       </c>
       <c r="I16" s="14">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J16" s="14">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="K16" s="15">
-        <v>-33.098591549295</v>
+        <v>-35.761589403973</v>
       </c>
       <c r="L16" s="15">
-        <v>-41.358024691358</v>
+        <v>-42.261904761904</v>
       </c>
       <c r="M16" s="15">
-        <v>-12.844036697247</v>
+        <v>-16.379310344827</v>
       </c>
       <c r="N16" s="15">
-        <v>-75.765306122449</v>
+        <v>-76.341463414634</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>14</v>
       </c>
       <c r="D17" s="14">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G17" s="14">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="H17" s="15">
-        <v>-31.884057971014</v>
+        <v>-6.557377049180</v>
       </c>
       <c r="I17" s="14">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="J17" s="14">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="K17" s="15">
-        <v>-20</v>
+        <v>-18.352059925093</v>
       </c>
       <c r="L17" s="15">
-        <v>-5.555555555555</v>
+        <v>-4.803493449781</v>
       </c>
       <c r="M17" s="15">
-        <v>94.285714285714</v>
+        <v>92.920353982300</v>
       </c>
       <c r="N17" s="15">
-        <v>1.492537313432</v>
+        <v>-0.909090909090</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,13 +1016,13 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F18" s="14">
         <v>15</v>
@@ -1034,22 +1034,22 @@
         <v>-28.571428571428</v>
       </c>
       <c r="I18" s="14">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="J18" s="14">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K18" s="15">
-        <v>11.956521739130</v>
+        <v>12.5</v>
       </c>
       <c r="L18" s="15">
-        <v>0</v>
+        <v>0.934579439252</v>
       </c>
       <c r="M18" s="15">
-        <v>53.731343283582</v>
+        <v>50</v>
       </c>
       <c r="N18" s="15">
-        <v>-77.008928571428</v>
+        <v>-77.070063694267</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G19" s="14">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H19" s="15">
-        <v>11.320754716981</v>
+        <v>6.896551724137</v>
       </c>
       <c r="I19" s="14">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="J19" s="14">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="K19" s="15">
-        <v>7.804878048780</v>
+        <v>6.363636363636</v>
       </c>
       <c r="L19" s="15">
-        <v>6.25</v>
+        <v>5.405405405405</v>
       </c>
       <c r="M19" s="15">
-        <v>132.631578947368</v>
+        <v>127.184466019417</v>
       </c>
       <c r="N19" s="15">
-        <v>46.357615894039</v>
+        <v>48.101265822784</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>4</v>
+      </c>
+      <c r="D20" s="14">
         <v>3</v>
       </c>
-      <c r="D20" s="14">
-        <v>9</v>
-      </c>
       <c r="E20" s="15">
-        <v>-66.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20" s="14">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H20" s="15">
-        <v>-63.333333333333</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I20" s="14">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J20" s="14">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K20" s="15">
-        <v>-19.047619047619</v>
+        <v>-17.241379310344</v>
       </c>
       <c r="L20" s="15">
-        <v>-20</v>
+        <v>-20.879120879120</v>
       </c>
       <c r="M20" s="15">
-        <v>94.285714285714</v>
+        <v>94.594594594594</v>
       </c>
       <c r="N20" s="15">
-        <v>-66</v>
+        <v>-66.511627906976</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D21" s="17">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="E21" s="18">
-        <v>-22.950819672131</v>
+        <v>-20.454545454545</v>
       </c>
       <c r="F21" s="17">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="G21" s="17">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="H21" s="18">
-        <v>-26.363636363636</v>
+        <v>-17.788461538461</v>
       </c>
       <c r="I21" s="17">
-        <v>705</v>
+        <v>743</v>
       </c>
       <c r="J21" s="17">
-        <v>796</v>
+        <v>840</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.432160804020</v>
+        <v>-11.547619047619</v>
       </c>
       <c r="L21" s="18">
-        <v>-9.961685823754</v>
+        <v>-10.157194679564</v>
       </c>
       <c r="M21" s="18">
-        <v>68.257756563245</v>
+        <v>65.478841870824</v>
       </c>
       <c r="N21" s="18">
-        <v>-50.595655220742</v>
+        <v>-50.892267019167</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1220,14 +1220,14 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>2</v>
-      </c>
-      <c r="D23" s="14">
-        <v>2</v>
-      </c>
-      <c r="E23" s="15">
-        <v>0</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
         <v>2</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E24" s="15">
-        <v>240</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="F24" s="14">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G24" s="14">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H24" s="15">
-        <v>23.75</v>
+        <v>32.894736842105</v>
       </c>
       <c r="I24" s="14">
-        <v>392</v>
+        <v>414</v>
       </c>
       <c r="J24" s="14">
-        <v>427</v>
+        <v>458</v>
       </c>
       <c r="K24" s="15">
-        <v>-8.196721311475</v>
+        <v>-9.606986899563</v>
       </c>
       <c r="L24" s="15">
-        <v>8.888888888888</v>
+        <v>7.8125</v>
       </c>
       <c r="M24" s="15">
-        <v>39.501779359430</v>
+        <v>37.086092715231</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>66.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F25" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G25" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H25" s="15">
-        <v>69.230769230769</v>
+        <v>50</v>
       </c>
       <c r="I25" s="14">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="J25" s="14">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="K25" s="15">
-        <v>-14.736842105263</v>
+        <v>-14.705882352941</v>
       </c>
       <c r="L25" s="15">
-        <v>-3.571428571428</v>
+        <v>0</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E26" s="15">
-        <v>16</v>
+        <v>-57.692307692307</v>
       </c>
       <c r="F26" s="14">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G26" s="14">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H26" s="15">
-        <v>-11.827956989247</v>
+        <v>-20.652173913043</v>
       </c>
       <c r="I26" s="14">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="J26" s="14">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="K26" s="15">
-        <v>-8.734939759036</v>
+        <v>-12.290502793296</v>
       </c>
       <c r="L26" s="15">
-        <v>3.412969283276</v>
+        <v>-1.875</v>
       </c>
       <c r="M26" s="15">
-        <v>8.602150537634</v>
+        <v>2.280130293159</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>3</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
+        <v>3</v>
+      </c>
+      <c r="G27" s="14">
         <v>5</v>
       </c>
-      <c r="G27" s="14">
-        <v>4</v>
-      </c>
       <c r="H27" s="15">
-        <v>25</v>
+        <v>-40</v>
       </c>
       <c r="I27" s="14">
         <v>15</v>
       </c>
       <c r="J27" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K27" s="15">
-        <v>-6.25</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L27" s="15">
         <v>-6.25</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
       <c r="E28" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F28" s="14">
+        <v>4</v>
+      </c>
+      <c r="G28" s="14">
+        <v>8</v>
+      </c>
+      <c r="H28" s="15">
         <v>-50</v>
-      </c>
-      <c r="F28" s="14">
-        <v>6</v>
-      </c>
-      <c r="G28" s="14">
-        <v>7</v>
-      </c>
-      <c r="H28" s="15">
-        <v>-14.285714285714</v>
       </c>
       <c r="I28" s="14">
         <v>27</v>
       </c>
       <c r="J28" s="14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K28" s="15">
-        <v>-18.181818181818</v>
+        <v>-20.588235294117</v>
       </c>
       <c r="L28" s="15">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1470,37 +1470,37 @@
         <v>20</v>
       </c>
       <c r="D29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="15">
         <v>-100</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="14">
         <v>5</v>
       </c>
       <c r="H29" s="15">
-        <v>-60</v>
+        <v>-80</v>
       </c>
       <c r="I29" s="14">
         <v>9</v>
       </c>
       <c r="J29" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K29" s="15">
-        <v>-18.181818181818</v>
+        <v>-25</v>
       </c>
       <c r="L29" s="15">
-        <v>28.571428571428</v>
+        <v>0</v>
       </c>
       <c r="M29" s="15">
         <v>-25</v>
       </c>
       <c r="N29" s="15">
-        <v>-71.875</v>
+        <v>-76.923076923076</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1511,45 +1511,45 @@
         <v>20</v>
       </c>
       <c r="D30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" s="15">
         <v>-100</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="14">
         <v>5</v>
       </c>
       <c r="H30" s="15">
-        <v>-60</v>
+        <v>-80</v>
       </c>
       <c r="I30" s="14">
         <v>8</v>
       </c>
       <c r="J30" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K30" s="15">
-        <v>-27.272727272727</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L30" s="15">
-        <v>14.285714285714</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M30" s="15">
         <v>-20</v>
       </c>
       <c r="N30" s="15">
-        <v>-71.428571428571</v>
+        <v>-76.470588235294</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
